--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0003T0006Z000C1N46_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0003T0006Z000C1N46_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.4899392178189</v>
+        <v>4.304615122895571</v>
       </c>
       <c r="D2" t="n">
-        <v>8.155990522670786</v>
+        <v>1.325348459934003</v>
       </c>
       <c r="E2" t="n">
-        <v>12.25790018749161</v>
+        <v>1.991908780467386</v>
       </c>
       <c r="F2" t="n">
-        <v>9.91510292648516</v>
+        <v>1.611204225553839</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>21.71508954597203</v>
+        <v>3.528702051220455</v>
       </c>
       <c r="D3" t="n">
-        <v>5.73395546568003</v>
+        <v>0.931767763173005</v>
       </c>
       <c r="E3" t="n">
-        <v>12.25790018749161</v>
+        <v>1.991908780467386</v>
       </c>
       <c r="F3" t="n">
-        <v>9.91510292648516</v>
+        <v>1.611204225553839</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>15.80724119149656</v>
+        <v>2.568676693618191</v>
       </c>
       <c r="D4" t="n">
-        <v>15.8267179142189</v>
+        <v>2.571841661060571</v>
       </c>
       <c r="E4" t="n">
-        <v>12.25790018749161</v>
+        <v>1.991908780467386</v>
       </c>
       <c r="F4" t="n">
-        <v>9.91510292648516</v>
+        <v>1.611204225553839</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>6.586248518304615</v>
+        <v>1.0702653842245</v>
       </c>
       <c r="D5" t="n">
-        <v>11.01540602195813</v>
+        <v>1.790003478568196</v>
       </c>
       <c r="E5" t="n">
-        <v>12.25790018749161</v>
+        <v>1.991908780467386</v>
       </c>
       <c r="F5" t="n">
-        <v>9.91510292648516</v>
+        <v>1.611204225553839</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.56270807709606</v>
+        <v>5.77894006252811</v>
       </c>
       <c r="D6" t="n">
-        <v>4.804794060646835</v>
+        <v>0.7807790348551108</v>
       </c>
       <c r="E6" t="n">
-        <v>12.25790018749161</v>
+        <v>1.991908780467386</v>
       </c>
       <c r="F6" t="n">
-        <v>9.91510292648516</v>
+        <v>1.611204225553839</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>38.12712228614236</v>
+        <v>6.195657371498133</v>
       </c>
       <c r="D7" t="n">
-        <v>17.61718436980693</v>
+        <v>2.862792460093627</v>
       </c>
       <c r="E7" t="n">
-        <v>12.25790018749161</v>
+        <v>1.991908780467386</v>
       </c>
       <c r="F7" t="n">
-        <v>9.91510292648516</v>
+        <v>1.611204225553839</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>34.93908541882235</v>
+        <v>5.677601380558633</v>
       </c>
       <c r="D8" t="n">
-        <v>10.12412024183382</v>
+        <v>1.645169539297996</v>
       </c>
       <c r="E8" t="n">
-        <v>12.25790018749161</v>
+        <v>1.991908780467386</v>
       </c>
       <c r="F8" t="n">
-        <v>9.91510292648516</v>
+        <v>1.611204225553839</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>50.768712448629</v>
+        <v>8.249915772902213</v>
       </c>
       <c r="D9" t="n">
-        <v>9.838432661532854</v>
+        <v>1.598745307499089</v>
       </c>
       <c r="E9" t="n">
-        <v>12.25790018749161</v>
+        <v>1.991908780467386</v>
       </c>
       <c r="F9" t="n">
-        <v>9.91510292648516</v>
+        <v>1.611204225553839</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>34.18296237432158</v>
+        <v>5.554731385827258</v>
       </c>
       <c r="D10" t="n">
-        <v>12.48253297104871</v>
+        <v>2.028411607795415</v>
       </c>
       <c r="E10" t="n">
-        <v>12.25790018749161</v>
+        <v>1.991908780467386</v>
       </c>
       <c r="F10" t="n">
-        <v>9.91510292648516</v>
+        <v>1.611204225553839</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>26.70665872754399</v>
+        <v>4.339832043225899</v>
       </c>
       <c r="D11" t="n">
-        <v>10.410288369426</v>
+        <v>1.691671860031724</v>
       </c>
       <c r="E11" t="n">
-        <v>12.25790018749161</v>
+        <v>1.991908780467386</v>
       </c>
       <c r="F11" t="n">
-        <v>9.91510292648516</v>
+        <v>1.611204225553839</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>35.76266624504719</v>
+        <v>5.811433264820169</v>
       </c>
       <c r="D12" t="n">
-        <v>14.13317284880528</v>
+        <v>2.296640587930858</v>
       </c>
       <c r="E12" t="n">
-        <v>12.25790018749161</v>
+        <v>1.991908780467386</v>
       </c>
       <c r="F12" t="n">
-        <v>9.91510292648516</v>
+        <v>1.611204225553839</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>20.57341614524587</v>
+        <v>3.343180123602454</v>
       </c>
       <c r="D13" t="n">
-        <v>21.27189032381269</v>
+        <v>3.456682177619563</v>
       </c>
       <c r="E13" t="n">
-        <v>12.25790018749161</v>
+        <v>1.991908780467386</v>
       </c>
       <c r="F13" t="n">
-        <v>9.91510292648516</v>
+        <v>1.611204225553839</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>45.94331543677884</v>
+        <v>7.465788758476561</v>
       </c>
       <c r="D14" t="n">
-        <v>2.596757964739435</v>
+        <v>0.4219731692701582</v>
       </c>
       <c r="E14" t="n">
-        <v>12.25790018749161</v>
+        <v>1.991908780467386</v>
       </c>
       <c r="F14" t="n">
-        <v>9.91510292648516</v>
+        <v>1.611204225553839</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>59.1662833055998</v>
+        <v>9.614521037159967</v>
       </c>
       <c r="D15" t="n">
-        <v>17.02319307583084</v>
+        <v>2.766268874822511</v>
       </c>
       <c r="E15" t="n">
-        <v>12.25790018749161</v>
+        <v>1.991908780467386</v>
       </c>
       <c r="F15" t="n">
-        <v>9.91510292648516</v>
+        <v>1.611204225553839</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>15.57268982634323</v>
+        <v>2.530562096780775</v>
       </c>
       <c r="D16" t="n">
-        <v>14.80194113949458</v>
+        <v>2.40531543516787</v>
       </c>
       <c r="E16" t="n">
-        <v>12.25790018749161</v>
+        <v>1.991908780467386</v>
       </c>
       <c r="F16" t="n">
-        <v>9.91510292648516</v>
+        <v>1.611204225553839</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>35.42958083624858</v>
+        <v>5.757306885890394</v>
       </c>
       <c r="D17" t="n">
-        <v>13.88366078011831</v>
+        <v>2.256094876769225</v>
       </c>
       <c r="E17" t="n">
-        <v>12.25790018749161</v>
+        <v>1.991908780467386</v>
       </c>
       <c r="F17" t="n">
-        <v>9.91510292648516</v>
+        <v>1.611204225553839</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>12.69772796839479</v>
+        <v>2.063380794864153</v>
       </c>
       <c r="D18" t="n">
-        <v>15.10908163131337</v>
+        <v>2.455225765088423</v>
       </c>
       <c r="E18" t="n">
-        <v>12.25790018749161</v>
+        <v>1.991908780467386</v>
       </c>
       <c r="F18" t="n">
-        <v>9.91510292648516</v>
+        <v>1.611204225553839</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>26.81147693992867</v>
+        <v>4.356865002738409</v>
       </c>
       <c r="D19" t="n">
-        <v>20.22965451287911</v>
+        <v>3.287318858342855</v>
       </c>
       <c r="E19" t="n">
-        <v>12.25790018749161</v>
+        <v>1.991908780467386</v>
       </c>
       <c r="F19" t="n">
-        <v>9.91510292648516</v>
+        <v>1.611204225553839</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>23.36757153517328</v>
+        <v>3.797230374465659</v>
       </c>
       <c r="D20" t="n">
-        <v>25.10901920569136</v>
+        <v>4.080215620924847</v>
       </c>
       <c r="E20" t="n">
-        <v>12.25790018749161</v>
+        <v>1.991908780467386</v>
       </c>
       <c r="F20" t="n">
-        <v>9.91510292648516</v>
+        <v>1.611204225553839</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>22.46298219007552</v>
+        <v>3.650234605887272</v>
       </c>
       <c r="D21" t="n">
-        <v>23.39566313985397</v>
+        <v>3.801795260226271</v>
       </c>
       <c r="E21" t="n">
-        <v>12.25790018749161</v>
+        <v>1.991908780467386</v>
       </c>
       <c r="F21" t="n">
-        <v>9.91510292648516</v>
+        <v>1.611204225553839</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>24.36171110294248</v>
+        <v>3.958778054228154</v>
       </c>
       <c r="D22" t="n">
-        <v>22.57232006472355</v>
+        <v>3.668002010517577</v>
       </c>
       <c r="E22" t="n">
-        <v>12.25790018749161</v>
+        <v>1.991908780467386</v>
       </c>
       <c r="F22" t="n">
-        <v>9.91510292648516</v>
+        <v>1.611204225553839</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>31.02116264289626</v>
+        <v>5.040938929470642</v>
       </c>
       <c r="D23" t="n">
-        <v>30.27424996583078</v>
+        <v>4.919565619447502</v>
       </c>
       <c r="E23" t="n">
-        <v>12.25790018749161</v>
+        <v>1.991908780467386</v>
       </c>
       <c r="F23" t="n">
-        <v>9.91510292648516</v>
+        <v>1.611204225553839</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>43.97765176619601</v>
+        <v>7.146368412006852</v>
       </c>
       <c r="D24" t="n">
-        <v>44.56694597466429</v>
+        <v>7.242128720882948</v>
       </c>
       <c r="E24" t="n">
-        <v>12.25790018749161</v>
+        <v>1.991908780467386</v>
       </c>
       <c r="F24" t="n">
-        <v>9.91510292648516</v>
+        <v>1.611204225553839</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>39.68841713682613</v>
+        <v>6.449367784734247</v>
       </c>
       <c r="D25" t="n">
-        <v>38.66509552175104</v>
+        <v>6.283078022284545</v>
       </c>
       <c r="E25" t="n">
-        <v>12.25790018749161</v>
+        <v>1.991908780467386</v>
       </c>
       <c r="F25" t="n">
-        <v>9.91510292648516</v>
+        <v>1.611204225553839</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
